--- a/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_MFH_until_2004_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_MFH_until_2004_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>11.4541853459797</v>
+        <v>6.033507340527649</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>32967.51979783345</v>
       </c>
       <c r="F2" t="n">
-        <v>11.4541853459797</v>
+        <v>5.29613165951408</v>
       </c>
       <c r="G2" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="H2" t="n">
-        <v>29.0914553396565</v>
+        <v>26.42586783756312</v>
       </c>
       <c r="I2" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="J2" t="n">
-        <v>30.14567547931304</v>
+        <v>26.42586783756312</v>
       </c>
       <c r="K2" t="n">
         <v>32967.51979783345</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>34.81854801264637</v>
+        <v>39.58686596825736</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>32967.51979783345</v>
       </c>
       <c r="F3" t="n">
-        <v>34.81854801264637</v>
+        <v>43.55935522847941</v>
       </c>
       <c r="G3" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="H3" t="n">
-        <v>43.11007293965652</v>
+        <v>42.52064320705411</v>
       </c>
       <c r="I3" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="J3" t="n">
-        <v>44.16429307931304</v>
+        <v>45.02096330735365</v>
       </c>
       <c r="K3" t="n">
         <v>32967.51979783345</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>69.60867100443724</v>
+        <v>47.08073403946045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>32967.51979783345</v>
       </c>
       <c r="F4" t="n">
-        <v>71.78827188868182</v>
+        <v>47.08073403946045</v>
       </c>
       <c r="G4" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="H4" t="n">
-        <v>81.62946398389714</v>
+        <v>62.10128912623855</v>
       </c>
       <c r="I4" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="J4" t="n">
-        <v>79.96145689298916</v>
+        <v>62.09560327396151</v>
       </c>
       <c r="K4" t="n">
         <v>32967.51979783345</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>69.60867100443727</v>
+        <v>47.08073403946046</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>32967.51979783345</v>
       </c>
       <c r="F5" t="n">
-        <v>71.78827188868182</v>
+        <v>47.08073403946045</v>
       </c>
       <c r="G5" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="H5" t="n">
-        <v>81.62946398389714</v>
+        <v>62.10128912623855</v>
       </c>
       <c r="I5" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="J5" t="n">
-        <v>79.96145689298918</v>
+        <v>62.09560327396151</v>
       </c>
       <c r="K5" t="n">
         <v>32967.51979783345</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>75.01043997098043</v>
+        <v>83.2565781123262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>32967.51979783345</v>
       </c>
       <c r="F6" t="n">
-        <v>75.92031424847626</v>
+        <v>80.54073400901643</v>
       </c>
       <c r="G6" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="H6" t="n">
-        <v>90.95153662885154</v>
+        <v>93.33098805918051</v>
       </c>
       <c r="I6" t="n">
         <v>32967.51979783345</v>
       </c>
       <c r="J6" t="n">
-        <v>89.79852845805593</v>
+        <v>89.97762671114982</v>
       </c>
       <c r="K6" t="n">
         <v>32967.51979783345</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>26.38114319523873</v>
+        <v>30.29906226024167</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>26.38114319523873</v>
+        <v>30.29906226024167</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>34.69206723512245</v>
+        <v>39.84425911016527</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>34.69206723512245</v>
+        <v>39.84425911016527</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>38.54625524166755</v>
+        <v>44.27084068431262</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>38.54625524166755</v>
+        <v>44.27084068431262</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>40.72085572292126</v>
+        <v>46.76839565700801</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>40.72085572292126</v>
+        <v>46.76839565700801</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>49.45127969675017</v>
+        <v>56.79539325842696</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>42.10658796073043</v>
+        <v>48.3599259041499</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>42.10658796073043</v>
+        <v>48.3599259041499</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009260328789000129</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.00947687542141879</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009483182494117649</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009476875421418783</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009483182494117649</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.009962809039314168</v>
+        <v>0.00947687542141879</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009483182494117649</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009070870211764706</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009962809039314168</v>
+        <v>0.00947687542141879</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.009895494776470587</v>
+        <v>0.009483182494117648</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3745069923814403</v>
+        <v>0.4380818</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>1.471954848</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3745069923814403</v>
+        <v>0.4336679766021782</v>
       </c>
       <c r="G17" t="n">
         <v>1.471954848</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2967739461907203</v>
+        <v>0.4188650264867576</v>
       </c>
       <c r="I17" t="n">
         <v>1.471954848</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2868906323814402</v>
+        <v>0.4113131867019811</v>
       </c>
       <c r="K17" t="n">
         <v>1.471954848</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3745069923814403</v>
+        <v>0.4380818</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>1.471954848</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3745069923814403</v>
+        <v>0.4336679766021782</v>
       </c>
       <c r="G18" t="n">
         <v>1.471954848</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2967739461907203</v>
+        <v>0.4223382077860652</v>
       </c>
       <c r="I18" t="n">
         <v>1.471954848</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2868906323814402</v>
+        <v>0.4113131867019811</v>
       </c>
       <c r="K18" t="n">
         <v>1.471954848</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3745069923814403</v>
+        <v>0.4380818</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>1.471954848</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3745069923814403</v>
+        <v>0.4336679766021782</v>
       </c>
       <c r="G19" t="n">
         <v>1.471954848</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2967739461907203</v>
+        <v>0.4223382077860652</v>
       </c>
       <c r="I19" t="n">
         <v>1.471954848</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2868906323814402</v>
+        <v>0.4113131867019811</v>
       </c>
       <c r="K19" t="n">
         <v>1.471954848</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2034231703548728</v>
+        <v>0.4261457971872818</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>1.471954848</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1894466375830874</v>
+        <v>0.4272217583518246</v>
       </c>
       <c r="G20" t="n">
         <v>1.471954848</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1242723995728696</v>
+        <v>0.3923864925786879</v>
       </c>
       <c r="I20" t="n">
         <v>1.471954848</v>
       </c>
       <c r="J20" t="n">
-        <v>0.13142454</v>
+        <v>0.39427362</v>
       </c>
       <c r="K20" t="n">
         <v>1.471954848</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2104145659076375</v>
+        <v>0.4261457971872818</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>1.471954848</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2022422713509268</v>
+        <v>0.4272217583518246</v>
       </c>
       <c r="G21" t="n">
         <v>1.471954848</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1242723995728696</v>
+        <v>0.3889133112793802</v>
       </c>
       <c r="I21" t="n">
         <v>1.471954848</v>
       </c>
       <c r="J21" t="n">
-        <v>0.13142454</v>
+        <v>0.3942736199999999</v>
       </c>
       <c r="K21" t="n">
         <v>1.471954848</v>
@@ -2142,13 +2142,13 @@
         <v>6.179579802768676</v>
       </c>
       <c r="H46" t="n">
-        <v>4.84734181076757</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>4.770115010147716</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>4.84734181076757</v>
       </c>
       <c r="K46" t="n">
         <v>4.770115010147716</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.9319246931502675</v>
+        <v>0.9482240994163054</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>8.044311364864901</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8883251308178469</v>
+        <v>0.8926678134986077</v>
       </c>
       <c r="G53" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="H53" t="n">
-        <v>1.594272743851576</v>
+        <v>1.670348801303714</v>
       </c>
       <c r="I53" t="n">
         <v>3.354127984796902</v>
       </c>
       <c r="J53" t="n">
-        <v>1.610107139078889</v>
+        <v>1.596252462826466</v>
       </c>
       <c r="K53" t="n">
         <v>3.354127984796902</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>2.016224117781257</v>
+        <v>1.95345977819245</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>8.044311364864901</v>
       </c>
       <c r="F54" t="n">
-        <v>1.977254500105923</v>
+        <v>1.92743314980156</v>
       </c>
       <c r="G54" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="H54" t="n">
-        <v>2.628334097098437</v>
+        <v>2.591343629395602</v>
       </c>
       <c r="I54" t="n">
         <v>3.916781821119674</v>
       </c>
       <c r="J54" t="n">
-        <v>2.669720492736557</v>
+        <v>2.5528413792264</v>
       </c>
       <c r="K54" t="n">
         <v>3.916781821119674</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>2.016224117781257</v>
+        <v>1.95345977819245</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>8.044311364864901</v>
       </c>
       <c r="F55" t="n">
-        <v>1.977254500105923</v>
+        <v>1.92743314980156</v>
       </c>
       <c r="G55" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="H55" t="n">
-        <v>2.628334097098437</v>
+        <v>2.591343629395602</v>
       </c>
       <c r="I55" t="n">
         <v>4.263138239944696</v>
       </c>
       <c r="J55" t="n">
-        <v>2.669720492736557</v>
+        <v>2.5528413792264</v>
       </c>
       <c r="K55" t="n">
         <v>4.263138239944696</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>2.049793308369698</v>
+        <v>1.948411454020263</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>8.044311364864901</v>
       </c>
       <c r="F56" t="n">
-        <v>1.9001962570878</v>
+        <v>1.878405371586142</v>
       </c>
       <c r="G56" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="H56" t="n">
-        <v>2.506193102243866</v>
+        <v>2.504202569985983</v>
       </c>
       <c r="I56" t="n">
         <v>4.495728428738632</v>
       </c>
       <c r="J56" t="n">
-        <v>2.626475224849707</v>
+        <v>2.470338680198181</v>
       </c>
       <c r="K56" t="n">
         <v>4.495728428738632</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.9958640066008064</v>
+        <v>0.3636580876495392</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>8.044311364864901</v>
       </c>
       <c r="F64" t="n">
-        <v>1.024616745131244</v>
+        <v>0.3896847160404294</v>
       </c>
       <c r="G64" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="H64" t="n">
-        <v>1.405263920882745</v>
+        <v>0.4601795300647828</v>
       </c>
       <c r="I64" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="J64" t="n">
-        <v>1.371696308483256</v>
+        <v>0.4986505575634132</v>
       </c>
       <c r="K64" t="n">
         <v>8.044311364864901</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9958640066008064</v>
+        <v>0.3688500625688796</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>8.044311364864901</v>
       </c>
       <c r="F65" t="n">
-        <v>1.024616745131244</v>
+        <v>0.3896847160404294</v>
       </c>
       <c r="G65" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="H65" t="n">
-        <v>1.405263920882745</v>
+        <v>0.4623571729385905</v>
       </c>
       <c r="I65" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="J65" t="n">
-        <v>1.371696308483256</v>
+        <v>0.5008775244571287</v>
       </c>
       <c r="K65" t="n">
         <v>8.044311364864901</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.039379716684097</v>
+        <v>0.3688500625688796</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>8.044311364864901</v>
       </c>
       <c r="F66" t="n">
-        <v>1.184711732290232</v>
+        <v>0.4495892640253134</v>
       </c>
       <c r="G66" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="H66" t="n">
-        <v>1.608568754597543</v>
+        <v>0.6336217095068806</v>
       </c>
       <c r="I66" t="n">
         <v>8.044311364864901</v>
       </c>
       <c r="J66" t="n">
-        <v>1.493691357792306</v>
+        <v>0.7006166266697178</v>
       </c>
       <c r="K66" t="n">
         <v>8.044311364864901</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1758563531522178</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1758563531522178</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3064816566169382</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3064816566169382</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4146152846879549</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4146152846879549</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5071605225913727</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5071605225913727</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5877635009919443</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5877635009919443</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="77">
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1758563531522178</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1758563531522178</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="78">
@@ -3329,13 +3329,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3064816566169382</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.3064816566169382</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="79">
@@ -3366,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4146152846879549</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.4146152846879549</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5071605225913727</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5071605225913727</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.5877635009919443</v>
+        <v>8.044311364864901</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5877635009919443</v>
+        <v>8.044311364864901</v>
       </c>
     </row>
     <row r="82">
